--- a/artfynd/A 2803-2020 artfynd.xlsx
+++ b/artfynd/A 2803-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118903219</v>
+        <v>118903046</v>
       </c>
       <c r="B2" t="n">
-        <v>91124</v>
+        <v>97846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689427</v>
+        <v>689418</v>
       </c>
       <c r="R2" t="n">
-        <v>6632646</v>
+        <v>6632677</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903046</v>
+        <v>118903065</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,55 +803,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Gårdagsmossberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689418</v>
+        <v>689435</v>
       </c>
       <c r="R3" t="n">
-        <v>6632677</v>
+        <v>6632618</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118903065</v>
+        <v>118903348</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
+        <v>103349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,49 +921,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdagsmossberget, Upl</t>
+          <t>Täfsorna (Täfsorna), Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689435</v>
+        <v>689478</v>
       </c>
       <c r="R4" t="n">
-        <v>6632618</v>
+        <v>6632603</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118903348</v>
+        <v>118903219</v>
       </c>
       <c r="B5" t="n">
-        <v>103349</v>
+        <v>91124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,34 +1023,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Täfsorna (Täfsorna), Upl</t>
+          <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689478</v>
+        <v>689427</v>
       </c>
       <c r="R5" t="n">
-        <v>6632603</v>
+        <v>6632646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2803-2020 artfynd.xlsx
+++ b/artfynd/A 2803-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118903046</v>
+        <v>118903348</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>103356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Täfsorna (Täfsorna), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689418</v>
+        <v>689478</v>
       </c>
       <c r="R2" t="n">
-        <v>6632677</v>
+        <v>6632603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903065</v>
+        <v>118903219</v>
       </c>
       <c r="B3" t="n">
-        <v>56502</v>
+        <v>91131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,49 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdagsmossberget, Upl</t>
+          <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689435</v>
+        <v>689427</v>
       </c>
       <c r="R3" t="n">
-        <v>6632618</v>
+        <v>6632646</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118903348</v>
+        <v>118903065</v>
       </c>
       <c r="B4" t="n">
-        <v>103349</v>
+        <v>56502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,37 +895,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Täfsorna (Täfsorna), Upl</t>
+          <t>Gårdagsmossberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689478</v>
+        <v>689435</v>
       </c>
       <c r="R4" t="n">
-        <v>6632603</v>
+        <v>6632618</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118903219</v>
+        <v>118903046</v>
       </c>
       <c r="B5" t="n">
-        <v>91124</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,38 +1005,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689427</v>
+        <v>689418</v>
       </c>
       <c r="R5" t="n">
-        <v>6632646</v>
+        <v>6632677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2803-2020 artfynd.xlsx
+++ b/artfynd/A 2803-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118903348</v>
+        <v>118903065</v>
       </c>
       <c r="B2" t="n">
-        <v>103356</v>
+        <v>56502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Täfsorna (Täfsorna), Upl</t>
+          <t>Gårdagsmossberget, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689478</v>
+        <v>689435</v>
       </c>
       <c r="R2" t="n">
-        <v>6632603</v>
+        <v>6632618</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903219</v>
+        <v>118903046</v>
       </c>
       <c r="B3" t="n">
-        <v>91131</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +801,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689427</v>
+        <v>689418</v>
       </c>
       <c r="R3" t="n">
-        <v>6632646</v>
+        <v>6632677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118903065</v>
+        <v>118903219</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
+        <v>91131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,49 +921,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdagsmossberget, Upl</t>
+          <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689435</v>
+        <v>689427</v>
       </c>
       <c r="R4" t="n">
-        <v>6632618</v>
+        <v>6632646</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118903046</v>
+        <v>118903348</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
+        <v>103356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,52 +1019,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Täfsorna (Täfsorna), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689418</v>
+        <v>689478</v>
       </c>
       <c r="R5" t="n">
-        <v>6632677</v>
+        <v>6632603</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
